--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,38 +896,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129341804</v>
+        <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>96960</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445901</v>
+        <v>445941</v>
       </c>
       <c r="R4" t="n">
-        <v>6537209</v>
+        <v>6537243</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129341768</v>
+        <v>129341714</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,16 +1026,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1035,32 +1043,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445941</v>
+        <v>445971</v>
       </c>
       <c r="R5" t="n">
-        <v>6537243</v>
+        <v>6537201</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,19 +1088,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,62 +1105,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129341714</v>
+        <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>90921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445971</v>
+        <v>446009</v>
       </c>
       <c r="R6" t="n">
-        <v>6537201</v>
+        <v>6537190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,48 +1214,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129341639</v>
+        <v>129340476</v>
       </c>
       <c r="B7" t="n">
-        <v>90921</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446009</v>
+        <v>445942</v>
       </c>
       <c r="R7" t="n">
-        <v>6537190</v>
+        <v>6537194</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,9 +1290,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,12 +1317,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1440,56 +1444,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129340476</v>
+        <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>96024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445942</v>
+        <v>446009</v>
       </c>
       <c r="R9" t="n">
-        <v>6537194</v>
+        <v>6537256</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,22 +1543,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341786</v>
+        <v>129341020</v>
       </c>
       <c r="B10" t="n">
-        <v>96024</v>
+        <v>8439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,41 +1566,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446009</v>
+        <v>445854</v>
       </c>
       <c r="R10" t="n">
-        <v>6537256</v>
+        <v>6537218</v>
       </c>
       <c r="S10" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1629,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,69 +1659,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R11" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,19 +1744,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,39 +1761,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129341438</v>
+        <v>129341227</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1811,24 +1802,28 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445960</v>
+        <v>445939</v>
       </c>
       <c r="R12" t="n">
-        <v>6537174</v>
+        <v>6537184</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,39 +1850,50 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129341227</v>
+        <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>96960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,46 +1901,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445939</v>
+        <v>445906</v>
       </c>
       <c r="R13" t="n">
-        <v>6537184</v>
+        <v>6537161</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,29 +1987,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129341805</v>
+        <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96960</v>
+        <v>96120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,28 +2016,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2044,13 +2044,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445906</v>
+        <v>446010</v>
       </c>
       <c r="R14" t="n">
-        <v>6537161</v>
+        <v>6537252</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,52 +2116,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129341794</v>
+        <v>129340658</v>
       </c>
       <c r="B15" t="n">
-        <v>96120</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446010</v>
+        <v>445935</v>
       </c>
       <c r="R15" t="n">
-        <v>6537252</v>
+        <v>6537213</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,19 +2189,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,62 +2206,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129340658</v>
+        <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>96167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445935</v>
+        <v>445849</v>
       </c>
       <c r="R16" t="n">
-        <v>6537213</v>
+        <v>6537220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129341161</v>
+        <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96167</v>
+        <v>96960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,21 +2326,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2364,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445849</v>
+        <v>445859</v>
       </c>
       <c r="R17" t="n">
-        <v>6537220</v>
+        <v>6537202</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129341045</v>
+        <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96960</v>
+        <v>96970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,19 +2441,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445859</v>
+        <v>445901</v>
       </c>
       <c r="R18" t="n">
-        <v>6537202</v>
+        <v>6537209</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2494,32 +2484,145 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129357642</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bronserud, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>446006</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6537240</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Elvira Klang, Johan Thulin, Malte Lindberg, Tilde Carlinger, Vera Malmqvist, Emilia Blixt, Klara Lindberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,60 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B2" t="n">
-        <v>96120</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R2" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +748,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,65 +765,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>96146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R3" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +857,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,57 +1555,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96120</v>
+        <v>96146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96970</v>
+        <v>96986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>96147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R2" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +755,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,72 +782,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>96146</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R3" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,19 +867,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96050</v>
+        <v>96051</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96146</v>
+        <v>96147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96052</v>
+        <v>96056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -1555,53 +1555,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R10" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,9 +1632,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,69 +1659,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R11" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,19 +1744,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B7" t="n">
         <v>57724</v>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R7" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1317,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B8" t="n">
         <v>57724</v>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R8" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96056</v>
+        <v>96058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,60 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B2" t="n">
-        <v>96154</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R2" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +748,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,65 +765,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>96158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R3" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +857,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90927</v>
+        <v>90931</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B7" t="n">
         <v>57724</v>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R7" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1317,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B8" t="n">
         <v>57724</v>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R8" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96058</v>
+        <v>96062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96154</v>
+        <v>96158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>96166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R2" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +755,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,72 +782,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>96158</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R3" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,19 +867,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90931</v>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96062</v>
+        <v>96070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,64 +1548,60 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96158</v>
+        <v>96166</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Johan Thulin, Emilia Blixt, Elvira Klang</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90932</v>
+        <v>90935</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96070</v>
+        <v>96073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,60 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B2" t="n">
-        <v>96169</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R2" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +748,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,65 +765,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>96169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R3" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +857,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1555,57 +1555,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>96169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R2" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +755,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,72 +782,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>96169</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R3" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,19 +867,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -1555,57 +1555,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129341714</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90935</v>
+        <v>90963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R7" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,22 +1317,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R8" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96073</v>
+        <v>96102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,57 +1555,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>129340658</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -1555,53 +1555,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>8439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R10" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,9 +1632,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,69 +1659,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R11" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,19 +1744,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57743</v>
+        <v>57748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129341714</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R7" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,22 +1317,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R8" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,57 +1555,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>129340658</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57748</v>
+        <v>57749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129341714</v>
       </c>
       <c r="B5" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R7" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,22 +1317,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R8" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>129340658</v>
       </c>
       <c r="B15" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,60 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B2" t="n">
-        <v>96211</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R2" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +748,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,65 +765,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>96216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R3" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +857,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
         <v>129341639</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>90975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B7" t="n">
         <v>57733</v>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R7" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1317,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B8" t="n">
         <v>57733</v>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R8" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,53 +1555,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>8439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R10" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,9 +1632,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,69 +1659,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R11" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,19 +1744,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
         <v>129341805</v>
       </c>
       <c r="B13" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129341794</v>
       </c>
       <c r="B14" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129341161</v>
       </c>
       <c r="B16" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129341045</v>
       </c>
       <c r="B17" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129341804</v>
       </c>
       <c r="B18" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129357642</v>
       </c>
       <c r="B19" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129341081</v>
+        <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>96216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445858</v>
+        <v>446019</v>
       </c>
       <c r="R2" t="n">
-        <v>6537202</v>
+        <v>6537243</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +755,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,72 +782,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129340238</v>
+        <v>129341081</v>
       </c>
       <c r="B3" t="n">
-        <v>96216</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446019</v>
+        <v>445858</v>
       </c>
       <c r="R3" t="n">
-        <v>6537243</v>
+        <v>6537202</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,19 +867,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1555,57 +1555,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1628,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,65 +1645,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>8439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1734,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129340476</v>
+        <v>129341766</v>
       </c>
       <c r="B7" t="n">
         <v>57733</v>
@@ -1242,28 +1242,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445942</v>
+        <v>445926</v>
       </c>
       <c r="R7" t="n">
-        <v>6537194</v>
+        <v>6537183</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1317,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129341766</v>
+        <v>129340476</v>
       </c>
       <c r="B8" t="n">
         <v>57733</v>
@@ -1357,28 +1357,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445926</v>
+        <v>445942</v>
       </c>
       <c r="R8" t="n">
-        <v>6537183</v>
+        <v>6537194</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1555,53 +1555,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341438</v>
+        <v>129341020</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>8439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445960</v>
+        <v>445854</v>
       </c>
       <c r="R10" t="n">
-        <v>6537174</v>
+        <v>6537218</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,9 +1632,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,69 +1659,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341020</v>
+        <v>129341438</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445854</v>
+        <v>445960</v>
       </c>
       <c r="R11" t="n">
-        <v>6537218</v>
+        <v>6537174</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,19 +1744,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,12 +1761,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>57867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57867</v>
+        <v>57875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>129341768</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 362-2023 artfynd.xlsx
+++ b/artfynd/A 362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129340238</v>
       </c>
       <c r="B2" t="n">
-        <v>96216</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,53 +794,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341081</v>
+        <v>129341794</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445858</v>
+        <v>446010</v>
       </c>
       <c r="R3" t="n">
-        <v>6537202</v>
+        <v>6537252</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +866,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,72 +893,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129341768</v>
+        <v>129341161</v>
       </c>
       <c r="B4" t="n">
-        <v>57897</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445941</v>
+        <v>445849</v>
       </c>
       <c r="R4" t="n">
-        <v>6537243</v>
+        <v>6537220</v>
       </c>
       <c r="S4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +973,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,65 +990,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129341714</v>
+        <v>129357642</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445971</v>
+        <v>446006</v>
       </c>
       <c r="R5" t="n">
-        <v>6537201</v>
+        <v>6537240</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,30 +1083,31 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Elvira Klang, Johan Thulin, Malte Lindberg, Tilde Carlinger, Vera Malmqvist, Emilia Blixt, Klara Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129341639</v>
+        <v>129341045</v>
       </c>
       <c r="B6" t="n">
-        <v>90975</v>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446009</v>
+        <v>445859</v>
       </c>
       <c r="R6" t="n">
-        <v>6537190</v>
+        <v>6537202</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,42 +1201,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129341766</v>
+        <v>129341804</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445926</v>
+        <v>445901</v>
       </c>
       <c r="R7" t="n">
-        <v>6537183</v>
+        <v>6537209</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,6 +1294,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,56 +1313,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129340476</v>
+        <v>129341805</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>97394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445942</v>
+        <v>445906</v>
       </c>
       <c r="R8" t="n">
-        <v>6537194</v>
+        <v>6537161</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1416,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1431,7 @@
         <v>129341786</v>
       </c>
       <c r="B9" t="n">
-        <v>96120</v>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129341020</v>
+        <v>129341639</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>91282</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,46 +1550,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>5685</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverkärret, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445854</v>
+        <v>446009</v>
       </c>
       <c r="R10" t="n">
-        <v>6537218</v>
+        <v>6537190</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1607,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,22 +1624,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129341438</v>
+        <v>129341768</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>57966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,16 +1647,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1699,25 +1664,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445960</v>
+        <v>445941</v>
       </c>
       <c r="R11" t="n">
-        <v>6537174</v>
+        <v>6537243</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,9 +1716,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129341227</v>
+        <v>129340476</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,16 +1766,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1802,12 +1784,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1817,13 +1798,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445939</v>
+        <v>445942</v>
       </c>
       <c r="R12" t="n">
-        <v>6537184</v>
+        <v>6537194</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,7 +1833,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1843,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,7 +1852,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1890,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129341805</v>
+        <v>129340658</v>
       </c>
       <c r="B13" t="n">
-        <v>97056</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,45 +1881,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445906</v>
+        <v>445935</v>
       </c>
       <c r="R13" t="n">
-        <v>6537161</v>
+        <v>6537213</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,19 +1943,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129341794</v>
+        <v>129341081</v>
       </c>
       <c r="B14" t="n">
-        <v>96216</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,41 +1983,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446010</v>
+        <v>445858</v>
       </c>
       <c r="R14" t="n">
-        <v>6537252</v>
+        <v>6537202</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,19 +2045,9 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,26 +2062,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129340658</v>
+        <v>129341438</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2147,7 +2105,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2156,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445935</v>
+        <v>445960</v>
       </c>
       <c r="R15" t="n">
-        <v>6537213</v>
+        <v>6537174</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129341161</v>
+        <v>129341714</v>
       </c>
       <c r="B16" t="n">
-        <v>96263</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,34 +2187,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näverkärret, Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445849</v>
+        <v>445971</v>
       </c>
       <c r="R16" t="n">
-        <v>6537220</v>
+        <v>6537201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129341045</v>
+        <v>129341766</v>
       </c>
       <c r="B17" t="n">
-        <v>97056</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,34 +2289,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näverkärret, Näverkärret, Vg</t>
+          <t>Bronserud, Bronserud, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445859</v>
+        <v>445926</v>
       </c>
       <c r="R17" t="n">
-        <v>6537202</v>
+        <v>6537183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,9 +2354,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,22 +2381,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129341804</v>
+        <v>129341227</v>
       </c>
       <c r="B18" t="n">
-        <v>97056</v>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,41 +2404,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bronserud, Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445901</v>
+        <v>445939</v>
       </c>
       <c r="R18" t="n">
-        <v>6537209</v>
+        <v>6537184</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2496,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,22 +2498,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Emilia Blixt, Johan Thulin, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129357642</v>
+        <v>129341020</v>
       </c>
       <c r="B19" t="n">
-        <v>96263</v>
+        <v>8444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,41 +2521,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bronserud, Vg</t>
+          <t>Näverkärret, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446006</v>
+        <v>445854</v>
       </c>
       <c r="R19" t="n">
-        <v>6537240</v>
+        <v>6537218</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2596,30 +2587,39 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Elvira Klang, Johan Thulin, Malte Lindberg, Tilde Carlinger, Vera Malmqvist, Emilia Blixt, Klara Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
